--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487814_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487814_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.4017</v>
+        <v>9.2376</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8533</v>
+        <v>8.4543</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5484</v>
+        <v>0.7833</v>
       </c>
       <c r="G2" t="n">
         <v>6.8928</v>
@@ -610,13 +610,13 @@
         <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.623</v>
+        <v>0.2129</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7053</v>
+        <v>-0.1043</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0823</v>
+        <v>0.3171</v>
       </c>
       <c r="V2" t="n">
         <v>0.467</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.1142</v>
+        <v>7.3714</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5212</v>
+        <v>6.3069</v>
       </c>
       <c r="F3" t="n">
-        <v>1.593</v>
+        <v>1.0645</v>
       </c>
       <c r="G3" t="n">
         <v>7.306</v>
@@ -688,13 +688,13 @@
         <v>2.0812</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4869</v>
+        <v>0.7441</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1396</v>
+        <v>-0.0747</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3473</v>
+        <v>0.8188</v>
       </c>
       <c r="V3" t="n">
         <v>-0.4706</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.576</v>
+        <v>4.0046</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8025</v>
+        <v>2.2312</v>
       </c>
       <c r="F4" t="n">
         <v>1.7734</v>
@@ -766,10 +766,10 @@
         <v>2.2893</v>
       </c>
       <c r="S4" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.5219</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6277</v>
+        <v>-0.199</v>
       </c>
       <c r="U4" t="n">
         <v>0.721</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3841</v>
+        <v>1.6777</v>
       </c>
       <c r="E5" t="n">
         <v>1.4194</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0353</v>
+        <v>0.2583</v>
       </c>
       <c r="G5" t="n">
         <v>0.0788</v>
@@ -844,13 +844,13 @@
         <v>2.0812</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1181</v>
+        <v>0.1755</v>
       </c>
       <c r="T5" t="n">
         <v>0.0867</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2048</v>
+        <v>0.0888</v>
       </c>
       <c r="V5" t="n">
         <v>0.5908</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. HAYES</t>
+          <t>A. LÓPEZ ÁLVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.232</v>
+        <v>0.1918</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8886</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6566</v>
+        <v>0.1918</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4362</v>
+        <v>0.1429</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6583</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2222</v>
+        <v>0.1429</v>
       </c>
       <c r="J6" t="n">
-        <v>3.261</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2422</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.0189</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8249</v>
+        <v>0.1429</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4162</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.2411</v>
+        <v>0.1429</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2893</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0812</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1197</v>
+        <v>0.0489</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5807</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.539</v>
+        <v>0.0489</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.1157</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3361</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. LÓPEZ ÁLVAREZ-TIRADOR</t>
+          <t>R. HAYES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1624</v>
+        <v>0.1017</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1.817</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1624</v>
+        <v>-1.7153</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1429</v>
+        <v>1.4362</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2.6583</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1429</v>
+        <v>-1.2222</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3.261</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2.2422</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.0189</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1429</v>
+        <v>-1.8249</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.4162</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1429</v>
+        <v>-2.2411</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.2893</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.0812</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0196</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.5091</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0196</v>
+        <v>0.4802</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.1157</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3361</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.4518</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1169</v>
+        <v>-0.4226</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.906</v>
+        <v>-1.2694</v>
       </c>
       <c r="F8" t="n">
-        <v>1.023</v>
+        <v>0.8468</v>
       </c>
       <c r="G8" t="n">
         <v>-1.421</v>
@@ -1078,13 +1078,13 @@
         <v>0.2081</v>
       </c>
       <c r="S8" t="n">
-        <v>0.976</v>
+        <v>0.4365</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2577</v>
+        <v>-0.1057</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7183</v>
+        <v>0.5422</v>
       </c>
       <c r="V8" t="n">
         <v>0.3538</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1515</v>
+        <v>-1.706</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3544</v>
+        <v>0.0323</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.797</v>
+        <v>-1.7383</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4697</v>
@@ -1156,13 +1156,13 @@
         <v>0.2081</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4299</v>
+        <v>0.0155</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.1228</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0796</v>
+        <v>0.1383</v>
       </c>
       <c r="V9" t="n">
         <v>-0.4599</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3341</v>
+        <v>-3.0802</v>
       </c>
       <c r="E10" t="n">
-        <v>1.4098</v>
+        <v>1.5169</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.7439</v>
+        <v>-4.5971</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9912</v>
@@ -1234,13 +1234,13 @@
         <v>0.6244</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4241</v>
+        <v>-0.1701</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3791</v>
+        <v>-0.2719</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.045</v>
+        <v>0.1018</v>
       </c>
       <c r="V10" t="n">
         <v>-2.3351</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5355</v>
+        <v>-3.4805</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2399</v>
+        <v>-3.0675</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2955</v>
+        <v>-0.413</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5717</v>
@@ -1312,13 +1312,13 @@
         <v>0.2081</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0907</v>
+        <v>-0.0357</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5219</v>
+        <v>-0.3495</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4313</v>
+        <v>0.3138</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.1525</v>
+        <v>-4.7555</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0754</v>
+        <v>-2.7958</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0771</v>
+        <v>-1.9597</v>
       </c>
       <c r="G12" t="n">
         <v>-3.3666</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6642</v>
+        <v>-0.2672</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4567</v>
+        <v>-0.1771</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2075</v>
+        <v>-0.09</v>
       </c>
       <c r="V12" t="n">
         <v>1.1675</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.813700000000004</v>
+        <v>9.139999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>14.3191</v>
+        <v>14.6453</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.5052</v>
+        <v>-5.5053</v>
       </c>
       <c r="G13" t="n">
         <v>9.614000000000001</v>
@@ -1468,13 +1468,13 @@
         <v>11.4465</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3455</v>
+        <v>2.6717</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1356</v>
+        <v>-0.8092</v>
       </c>
       <c r="U13" t="n">
-        <v>3.4811</v>
+        <v>3.4809</v>
       </c>
       <c r="V13" t="n">
         <v>-2.1052</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3317</v>
+        <v>1.5333</v>
       </c>
       <c r="E14" t="n">
         <v>3.0461</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7144</v>
+        <v>-1.5128</v>
       </c>
       <c r="G14" t="n">
         <v>-3.2355</v>
@@ -1546,13 +1546,13 @@
         <v>2.2893</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2871</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="T14" t="n">
         <v>-0.37</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0829</v>
+        <v>0.2845</v>
       </c>
       <c r="V14" t="n">
         <v>2.565</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0196</v>
+        <v>0.2495</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0534</v>
+        <v>1.2677</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.073</v>
+        <v>-1.0182</v>
       </c>
       <c r="G15" t="n">
         <v>0.1132</v>
@@ -1624,13 +1624,13 @@
         <v>1.6649</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6302</v>
+        <v>-0.3611</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0439</v>
+        <v>-0.8296</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4137</v>
+        <v>0.4685</v>
       </c>
       <c r="V15" t="n">
         <v>-1.1675</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>G. CLARKE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5788</v>
+        <v>-0.2057</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.7166</v>
+        <v>4.2196</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1378</v>
+        <v>-4.4253</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9617</v>
+        <v>1.0171</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3902</v>
+        <v>-1.8486</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5715</v>
+        <v>2.8656</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.3904</v>
+        <v>5.3975</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.676</v>
+        <v>-0.4929</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7144</v>
+        <v>5.8905</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4286</v>
+        <v>-4.3804</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2857</v>
+        <v>-1.3556</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1429</v>
+        <v>-3.0248</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6244</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6244</v>
+        <v>1.0406</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2414</v>
+        <v>-0.306</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3262</v>
+        <v>-0.2643</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0848</v>
+        <v>-0.0417</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1238</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.0437</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. DIBBA</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6965</v>
+        <v>-0.4423</v>
       </c>
       <c r="E17" t="n">
-        <v>0.151</v>
+        <v>-1.6094</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8475</v>
+        <v>1.1672</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.1849</v>
+        <v>-0.9617</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8868</v>
+        <v>-0.3902</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.2981</v>
+        <v>-0.5715</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5177</v>
+        <v>-1.3904</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3218</v>
+        <v>-0.676</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1959</v>
+        <v>-0.7144</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.7026</v>
+        <v>0.4286</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2086</v>
+        <v>0.2857</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.494</v>
+        <v>0.1429</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8731</v>
+        <v>0.6244</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4666</v>
+        <v>-0.1049</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2545</v>
+        <v>-0.2191</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2121</v>
+        <v>0.1142</v>
       </c>
       <c r="V17" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.4599</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. BILALOVIC</t>
+          <t>N. DEDOVIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1631</v>
+        <v>-0.6169</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4741</v>
+        <v>3.1981</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6372</v>
+        <v>-3.815</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.2764</v>
+        <v>1.8969</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.3965</v>
+        <v>0.433</v>
       </c>
       <c r="I18" t="n">
-        <v>0.12</v>
+        <v>1.4638</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3937</v>
+        <v>6.7182</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4693</v>
+        <v>1.8377</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8631</v>
+        <v>4.8806</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.6702</v>
+        <v>-4.8213</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.9271</v>
+        <v>-1.4046</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.7431</v>
+        <v>-3.4167</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6244</v>
+        <v>-2.2893</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0406</v>
+        <v>-4.1624</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S18" t="n">
-        <v>0.259</v>
+        <v>-0.2244</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.109</v>
+        <v>-0.5252</v>
       </c>
       <c r="U18" t="n">
-        <v>0.368</v>
+        <v>0.3008</v>
       </c>
       <c r="V18" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.23</v>
+        <v>1.1675</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. CLARKE</t>
+          <t>M. BILALOVIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2136</v>
+        <v>-1.2933</v>
       </c>
       <c r="E19" t="n">
-        <v>3.791</v>
+        <v>0.2598</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.0046</v>
+        <v>-1.5531</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0171</v>
+        <v>-2.2764</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8486</v>
+        <v>-2.3965</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8656</v>
+        <v>0.12</v>
       </c>
       <c r="J19" t="n">
-        <v>5.3975</v>
+        <v>1.3937</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4929</v>
+        <v>-0.4693</v>
       </c>
       <c r="L19" t="n">
-        <v>5.8905</v>
+        <v>1.8631</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.3804</v>
+        <v>-3.6702</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3556</v>
+        <v>-1.9271</v>
       </c>
       <c r="O19" t="n">
-        <v>-3.0248</v>
+        <v>-1.7431</v>
       </c>
       <c r="P19" t="n">
+        <v>0.6244</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-1.0406</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-2.0812</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.314</v>
+        <v>0.1288</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6929</v>
+        <v>-0.3233</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6211</v>
+        <v>0.4522</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1238</v>
+        <v>0.23</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0437</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. DEDOVIC</t>
+          <t>L. DIBBA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2431</v>
+        <v>-2.0156</v>
       </c>
       <c r="E20" t="n">
-        <v>2.7695</v>
+        <v>-1.1349</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.0127</v>
+        <v>-0.8807</v>
       </c>
       <c r="G20" t="n">
-        <v>1.8969</v>
+        <v>-2.1849</v>
       </c>
       <c r="H20" t="n">
-        <v>0.433</v>
+        <v>-0.8868</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4638</v>
+        <v>-1.2981</v>
       </c>
       <c r="J20" t="n">
-        <v>6.7182</v>
+        <v>0.5177</v>
       </c>
       <c r="K20" t="n">
-        <v>1.8377</v>
+        <v>0.3218</v>
       </c>
       <c r="L20" t="n">
-        <v>4.8806</v>
+        <v>0.1959</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.8213</v>
+        <v>-2.7026</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4046</v>
+        <v>-1.2086</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.4167</v>
+        <v>-1.494</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.2893</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.1624</v>
+        <v>-2.0812</v>
       </c>
       <c r="R20" t="n">
         <v>1.8731</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8507</v>
+        <v>0.1474</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9539</v>
+        <v>-0.0314</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1031</v>
+        <v>0.1788</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1675</v>
+        <v>0.4599</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. OKAFOR</t>
+          <t>A. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.514</v>
+        <v>-2.1539</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5582</v>
+        <v>-1.2907</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0442</v>
+        <v>-0.8633</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4967</v>
+        <v>-3.4858</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7802</v>
+        <v>-1.7591</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2769</v>
+        <v>-1.7267</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6109</v>
+        <v>-1.1752</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7395</v>
+        <v>-1.3712</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3504</v>
+        <v>0.1959</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1142</v>
+        <v>-2.3106</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0407</v>
+        <v>-0.3879</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0735</v>
+        <v>-1.9227</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0406</v>
+        <v>0.4162</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1422</v>
+        <v>-0.0427</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7829</v>
+        <v>-0.2424</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6407</v>
+        <v>0.1997</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8751</v>
+        <v>1.999</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.1238</v>
+        <v>1.1675</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7513</v>
+        <v>0.8314</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. LATORRE SANCHEZ</t>
+          <t>O. OKAFOR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7166</v>
+        <v>-2.4401</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.505</v>
+        <v>-2.451</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2116</v>
+        <v>0.0109</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.4858</v>
+        <v>-0.4967</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7591</v>
+        <v>0.7802</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7267</v>
+        <v>-1.2769</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1752</v>
+        <v>-0.6109</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.3712</v>
+        <v>0.7395</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1959</v>
+        <v>-1.3504</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.3106</v>
+        <v>0.1142</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3879</v>
+        <v>0.0407</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.9227</v>
+        <v>0.0735</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6244</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4162</v>
+        <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6054</v>
+        <v>-0.0683</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4567</v>
+        <v>-0.6758</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1487</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>1.999</v>
+        <v>-1.8751</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1675</v>
+        <v>-0.1238</v>
       </c>
       <c r="X22" t="n">
-        <v>0.8314</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="23">
@@ -2203,22 +2203,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.813599999999999</v>
+        <v>-7.385</v>
       </c>
       <c r="E23" t="n">
         <v>5.5053</v>
       </c>
       <c r="F23" t="n">
-        <v>-14.319</v>
+        <v>-12.8903</v>
       </c>
       <c r="G23" t="n">
-        <v>-9.613799999999999</v>
+        <v>-9.613800000000001</v>
       </c>
       <c r="H23" t="n">
         <v>-5.5115</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.1026</v>
+        <v>-4.102599999999999</v>
       </c>
       <c r="J23" t="n">
         <v>13.7989</v>
@@ -2248,13 +2248,13 @@
         <v>12.4871</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.345400000000001</v>
+        <v>-0.9167</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.481</v>
+        <v>-3.4811</v>
       </c>
       <c r="U23" t="n">
-        <v>1.1355</v>
+        <v>2.5644</v>
       </c>
       <c r="V23" t="n">
         <v>2.1052</v>
